--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-14 12:00:00</t>
+          <t>2026-09-14 09:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:00</t>
+          <t>2026-09-14 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-14 14:30:00</t>
+          <t>2026-09-14 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-14 14:45:00</t>
+          <t>2026-09-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:00</t>
+          <t>2026-09-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:00</t>
+          <t>2026-09-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-14 15:45:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-14 16:15:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-14 16:45:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,156 +3685,7654 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Georgia Erovnuli Liga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dinamo Tbilisi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gagra</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Masr</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Olympic El Qanah</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>National Bank of Egypt</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Porto II</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FC Vizela</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sporting CP II</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lusitania Lourosa</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zemun</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Radnik Surdulica</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Piast Gliwice</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>United Nordic</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Norrby</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kayserispor</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>İstanbulspor</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mladost DG</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Budućnost</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mornar</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Otrant-Olympic</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Petrovac</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Arsenal Tivat</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cyprus First Division</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Digenis Ypsonas</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Septemvri Sofia</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rio Ave FC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Petrolul 52</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Utrecht II</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ajax II</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PSV II</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AZ II</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Celta de Vigo II</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SD Eibar</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>St Patrick's Athl.</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>2.1</v>
+      </c>
+      <c r="O57">
+        <v>3.8</v>
+      </c>
+      <c r="P57">
+        <v>3.59</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>1.66</v>
+      </c>
+      <c r="AB57">
+        <v>2.2</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Unión San Felipe</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>1.52</v>
+      </c>
+      <c r="O64">
+        <v>4.16</v>
+      </c>
+      <c r="P64">
+        <v>6.89</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>1.85</v>
+      </c>
+      <c r="AB64">
+        <v>1.95</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>2026-09-14 21:30:00</t>
         </is>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G8">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G39">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G51">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G53">

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G47">

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-14 12:30:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-14 12:45:00</t>
+          <t>2026-09-14 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-14 13:00:00</t>
+          <t>2026-09-14 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:00</t>
+          <t>2026-09-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G37">

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-14 12:00:00</t>
+          <t>2026-09-14 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1245,22 +1245,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6">
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-14 12:30:00</t>
+          <t>2026-09-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-14 12:45:00</t>
+          <t>2026-09-14 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-14 13:00:00</t>
+          <t>2026-09-14 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:00</t>
+          <t>2026-09-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="P20">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,22 +4179,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G40">
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:00</t>
+          <t>2026-09-14 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-14 14:30:00</t>
+          <t>2026-09-14 14:05:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-14 14:45:00</t>
+          <t>2026-09-14 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:00</t>
+          <t>2026-09-14 14:45:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-14 15:30:00</t>
+          <t>2026-09-14 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G49">
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-14 15:45:00</t>
+          <t>2026-09-14 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G55">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:00</t>
+          <t>2026-09-14 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:15:00</t>
+          <t>2026-09-14 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-14 16:45:00</t>
+          <t>2026-09-14 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-14 18:00:00</t>
+          <t>2026-09-14 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-14 18:00:00</t>
+          <t>2026-09-14 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 18:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 18:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-14 20:00:00</t>
+          <t>2026-09-14 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-14 20:30:00</t>
+          <t>2026-09-14 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-14 20:30:00</t>
+          <t>2026-09-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,156 +11183,482 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-09-14 21:30:00</t>
         </is>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>5.08</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>8.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="P21">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -7176,10 +7176,10 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -7188,31 +7188,31 @@
         <v>0</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -8655,31 +8655,31 @@
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -8806,10 +8806,10 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -8969,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -8981,31 +8981,31 @@
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -9144,31 +9144,31 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -11509,156 +11509,319 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>1.37</v>
+      </c>
+      <c r="O69">
+        <v>4.3</v>
+      </c>
+      <c r="P69">
+        <v>7.25</v>
+      </c>
+      <c r="Q69">
+        <v>1.8</v>
+      </c>
+      <c r="R69">
+        <v>2.38</v>
+      </c>
+      <c r="S69">
+        <v>1.32</v>
+      </c>
+      <c r="T69">
+        <v>2.97</v>
+      </c>
+      <c r="U69">
+        <v>2.63</v>
+      </c>
+      <c r="V69">
+        <v>1.44</v>
+      </c>
+      <c r="W69">
+        <v>1.09</v>
+      </c>
+      <c r="X69">
+        <v>1.04</v>
+      </c>
+      <c r="Y69">
+        <v>1.22</v>
+      </c>
+      <c r="Z69">
+        <v>3.7</v>
+      </c>
+      <c r="AA69">
+        <v>1.75</v>
+      </c>
+      <c r="AB69">
+        <v>1.95</v>
+      </c>
+      <c r="AC69">
+        <v>2.9</v>
+      </c>
+      <c r="AD69">
+        <v>1.33</v>
+      </c>
+      <c r="AE69">
+        <v>1.13</v>
+      </c>
+      <c r="AF69">
+        <v>1.85</v>
+      </c>
+      <c r="AG69">
+        <v>1.8</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.2</v>
+      </c>
+      <c r="AK69">
+        <v>2.67</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-09-14 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-09-14 21:30:00</t>
         </is>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G51">
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -8655,31 +8655,31 @@
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA51">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -8806,10 +8806,10 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
         <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G53">
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.2</v>
+        <v>3.45</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -8969,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -8981,31 +8981,31 @@
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G54">
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -9144,31 +9144,31 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z54">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB54">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AC54">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF54">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL54">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -7991,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -8003,31 +8003,31 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -8154,10 +8154,10 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -8166,31 +8166,31 @@
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9772,34 +9772,34 @@
         <v>3.59</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA58">
         <v>1.66</v>
@@ -9808,19 +9808,19 @@
         <v>2.2</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R47">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -7991,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="V47">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -8003,31 +8003,31 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA47">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB47">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AC47">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AD47">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AE47">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF47">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AG47">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
+        <v>2.92</v>
+      </c>
+      <c r="Q48">
         <v>2.55</v>
       </c>
-      <c r="Q48">
-        <v>2.6</v>
-      </c>
       <c r="R48">
+        <v>2.55</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>2</v>
+      </c>
+      <c r="V48">
+        <v>1.68</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>1.09</v>
+      </c>
+      <c r="Z48">
+        <v>6</v>
+      </c>
+      <c r="AA48">
+        <v>1.4</v>
+      </c>
+      <c r="AB48">
         <v>2.7</v>
       </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>1.81</v>
-      </c>
-      <c r="V48">
-        <v>1.86</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>1.05</v>
-      </c>
-      <c r="Z48">
-        <v>7.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.28</v>
-      </c>
-      <c r="AB48">
-        <v>3.3</v>
-      </c>
       <c r="AC48">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD48">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AE48">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AF48">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AG48">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10448,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11076,34 +11076,34 @@
         <v>6.89</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA66">
         <v>1.85</v>
@@ -11112,19 +11112,19 @@
         <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="P20">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q20">
-        <v>5.75</v>
+        <v>1.67</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK20">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>5.08</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>8.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
-        <v>1.67</v>
+        <v>5.75</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21">
+        <v>1.28</v>
+      </c>
+      <c r="Z21">
+        <v>3.55</v>
+      </c>
+      <c r="AA21">
+        <v>2.2</v>
+      </c>
+      <c r="AB21">
+        <v>1.66</v>
+      </c>
+      <c r="AC21">
+        <v>3.1</v>
+      </c>
+      <c r="AD21">
+        <v>1.33</v>
+      </c>
+      <c r="AE21">
+        <v>1.1</v>
+      </c>
+      <c r="AF21">
+        <v>1.91</v>
+      </c>
+      <c r="AG21">
+        <v>1.83</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.2</v>
       </c>
-      <c r="Z21">
-        <v>4</v>
-      </c>
-      <c r="AA21">
-        <v>1.9</v>
-      </c>
-      <c r="AB21">
-        <v>1.9</v>
-      </c>
-      <c r="AC21">
-        <v>2.8</v>
-      </c>
-      <c r="AD21">
-        <v>1.42</v>
-      </c>
-      <c r="AE21">
-        <v>1.15</v>
-      </c>
-      <c r="AF21">
-        <v>2.3</v>
-      </c>
-      <c r="AG21">
-        <v>1.57</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.05</v>
-      </c>
       <c r="AK21">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="P4">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -976,13 +976,13 @@
         <v>1.84</v>
       </c>
       <c r="S4">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V4">
         <v>1.2</v>
@@ -991,25 +991,25 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y4">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Z4">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AA4">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AB4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1622,13 +1622,13 @@
         <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="R8">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="S8">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
         <v>2.57</v>
@@ -1652,7 +1652,7 @@
         <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
         <v>1.58</v>
@@ -1670,7 +1670,7 @@
         <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="U9">
         <v>2.74</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1809,22 +1809,22 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
         <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
         <v>3.28</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE9">
         <v>1.06</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -1954,10 +1954,10 @@
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1969,16 +1969,16 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
         <v>1.96</v>
@@ -1987,16 +1987,16 @@
         <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>5.08</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>8.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
-        <v>1.67</v>
+        <v>5.75</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20">
+        <v>1.28</v>
+      </c>
+      <c r="Z20">
+        <v>3.55</v>
+      </c>
+      <c r="AA20">
+        <v>2.2</v>
+      </c>
+      <c r="AB20">
+        <v>1.66</v>
+      </c>
+      <c r="AC20">
+        <v>3.1</v>
+      </c>
+      <c r="AD20">
+        <v>1.33</v>
+      </c>
+      <c r="AE20">
+        <v>1.1</v>
+      </c>
+      <c r="AF20">
+        <v>1.91</v>
+      </c>
+      <c r="AG20">
+        <v>1.83</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.2</v>
       </c>
-      <c r="Z20">
-        <v>4</v>
-      </c>
-      <c r="AA20">
-        <v>1.9</v>
-      </c>
-      <c r="AB20">
-        <v>1.9</v>
-      </c>
-      <c r="AC20">
-        <v>2.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.42</v>
-      </c>
-      <c r="AE20">
-        <v>1.15</v>
-      </c>
-      <c r="AF20">
-        <v>2.3</v>
-      </c>
-      <c r="AG20">
-        <v>1.57</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.05</v>
-      </c>
       <c r="AK20">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="P21">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q21">
-        <v>5.75</v>
+        <v>1.67</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="U21">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK21">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G51">
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>3.45</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -8655,31 +8655,31 @@
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB51">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG51">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -8969,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -8981,31 +8981,31 @@
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
+        <v>1.8</v>
+      </c>
+      <c r="AB53">
+        <v>1.87</v>
+      </c>
+      <c r="AC53">
+        <v>3.1</v>
+      </c>
+      <c r="AD53">
+        <v>1.32</v>
+      </c>
+      <c r="AE53">
+        <v>1.09</v>
+      </c>
+      <c r="AF53">
         <v>1.73</v>
       </c>
-      <c r="AB53">
-        <v>1.95</v>
-      </c>
-      <c r="AC53">
-        <v>2.88</v>
-      </c>
-      <c r="AD53">
-        <v>1.35</v>
-      </c>
-      <c r="AE53">
-        <v>1.11</v>
-      </c>
-      <c r="AF53">
-        <v>1.58</v>
-      </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q13">
         <v>2.88</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q31">
         <v>3.38</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q42">
         <v>2.38</v>
@@ -7170,10 +7170,10 @@
         <v>2.38</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U42">
         <v>2.33</v>
@@ -7182,7 +7182,7 @@
         <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -7650,10 +7650,10 @@
         <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
         <v>2.1</v>
@@ -7662,43 +7662,43 @@
         <v>1.41</v>
       </c>
       <c r="T45">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U45">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
+        <v>1.07</v>
+      </c>
+      <c r="X45">
         <v>1.03</v>
-      </c>
-      <c r="X45">
-        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="AA45">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="AB45">
         <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AD45">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
         <v>1.96</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK45">
         <v>1.4</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
+        <v>2.92</v>
+      </c>
+      <c r="Q47">
         <v>2.55</v>
       </c>
-      <c r="Q47">
-        <v>2.6</v>
-      </c>
       <c r="R47">
+        <v>2.55</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>2</v>
+      </c>
+      <c r="V47">
+        <v>1.68</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>1.09</v>
+      </c>
+      <c r="Z47">
+        <v>6</v>
+      </c>
+      <c r="AA47">
+        <v>1.4</v>
+      </c>
+      <c r="AB47">
         <v>2.7</v>
       </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>1.81</v>
-      </c>
-      <c r="V47">
-        <v>1.86</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>1.05</v>
-      </c>
-      <c r="Z47">
-        <v>7.5</v>
-      </c>
-      <c r="AA47">
-        <v>1.28</v>
-      </c>
-      <c r="AB47">
-        <v>3.3</v>
-      </c>
       <c r="AC47">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD47">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AE47">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AF47">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AG47">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q48">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R48">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -8154,10 +8154,10 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="V48">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -8166,31 +8166,31 @@
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z48">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA48">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB48">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AC48">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AD48">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AE48">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF48">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AG48">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G53">
@@ -8957,56 +8957,56 @@
         <v>0</v>
       </c>
       <c r="Q53">
+        <v>3.35</v>
+      </c>
+      <c r="R53">
+        <v>2.16</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>2.4</v>
+      </c>
+      <c r="V53">
+        <v>1.46</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>1.19</v>
+      </c>
+      <c r="Z53">
+        <v>4.1</v>
+      </c>
+      <c r="AA53">
+        <v>1.68</v>
+      </c>
+      <c r="AB53">
+        <v>2.02</v>
+      </c>
+      <c r="AC53">
+        <v>2.7</v>
+      </c>
+      <c r="AD53">
+        <v>1.4</v>
+      </c>
+      <c r="AE53">
+        <v>1.12</v>
+      </c>
+      <c r="AF53">
+        <v>1.55</v>
+      </c>
+      <c r="AG53">
         <v>2.2</v>
       </c>
-      <c r="R53">
-        <v>2.2</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>2.55</v>
-      </c>
-      <c r="V53">
-        <v>1.42</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>1.23</v>
-      </c>
-      <c r="Z53">
-        <v>3.65</v>
-      </c>
-      <c r="AA53">
-        <v>1.8</v>
-      </c>
-      <c r="AB53">
-        <v>1.87</v>
-      </c>
-      <c r="AC53">
-        <v>3.1</v>
-      </c>
-      <c r="AD53">
-        <v>1.32</v>
-      </c>
-      <c r="AE53">
-        <v>1.09</v>
-      </c>
-      <c r="AF53">
-        <v>1.73</v>
-      </c>
-      <c r="AG53">
-        <v>1.93</v>
-      </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G54">
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R54">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -9144,31 +9144,31 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB54">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AC54">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD54">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE54">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q59">
         <v>1.6</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -3898,13 +3898,13 @@
         <v>2.36</v>
       </c>
       <c r="O22">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R22">
         <v>2.4</v>
@@ -3913,13 +3913,13 @@
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3928,22 +3928,22 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC22">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE22">
         <v>1.16</v>
@@ -3952,7 +3952,7 @@
         <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P65">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S65">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T65">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U65">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="V65">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z65">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="AA65">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB65">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG65">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O4">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="Q4">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
         <v>1.84</v>
@@ -988,25 +988,25 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y4">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Z4">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AA4">
-        <v>2.92</v>
+        <v>3.24</v>
       </c>
       <c r="AB4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6.37</v>
       </c>
       <c r="AD4">
         <v>1.07</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
         <v>1.38</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="S8">
         <v>1.48</v>
@@ -1655,7 +1655,7 @@
         <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC8">
         <v>4.1</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
         <v>3.55</v>
@@ -1794,7 +1794,7 @@
         <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
         <v>2.74</v>
@@ -1942,22 +1942,22 @@
         <v>1.73</v>
       </c>
       <c r="O10">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1978,16 +1978,16 @@
         <v>3.55</v>
       </c>
       <c r="AA10">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
         <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="R12">
         <v>1.96</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T12">
         <v>2.47</v>
@@ -2292,7 +2292,7 @@
         <v>1.31</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2310,7 +2310,7 @@
         <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD12">
         <v>1.19</v>
@@ -2319,10 +2319,10 @@
         <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG12">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2920,16 +2920,16 @@
         <v>3</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
         <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.86</v>
+        <v>3.49</v>
       </c>
       <c r="R16">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2938,43 +2938,43 @@
         <v>2.81</v>
       </c>
       <c r="U16">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC16">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P17">
         <v>1.9</v>
       </c>
       <c r="Q17">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
         <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U17">
         <v>2.74</v>
@@ -3116,13 +3116,13 @@
         <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="AA17">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>3.28</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
         <v>3.7</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R19">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U19">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3442,28 +3442,28 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
         <v>3.82</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="Q20">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S20">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U20">
         <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="O21">
-        <v>5.08</v>
+        <v>6.25</v>
       </c>
       <c r="P21">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="Q21">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="S21">
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AC21">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG21">
         <v>1.57</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
         <v>3.45</v>
@@ -3913,7 +3913,7 @@
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
         <v>2.3</v>
@@ -3922,7 +3922,7 @@
         <v>1.55</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.03</v>
@@ -3931,7 +3931,7 @@
         <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA22">
         <v>1.61</v>
@@ -3946,13 +3946,13 @@
         <v>1.5</v>
       </c>
       <c r="AE22">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF22">
         <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P23">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q23">
         <v>5.75</v>
@@ -4073,49 +4073,49 @@
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
         <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="AD23">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
+        <v>2.8</v>
+      </c>
+      <c r="P26">
         <v>2.75</v>
       </c>
-      <c r="P26">
-        <v>2.82</v>
-      </c>
       <c r="Q26">
+        <v>3.36</v>
+      </c>
+      <c r="R26">
+        <v>1.95</v>
+      </c>
+      <c r="S26">
+        <v>1.5</v>
+      </c>
+      <c r="T26">
+        <v>2.24</v>
+      </c>
+      <c r="U26">
         <v>3.3</v>
       </c>
-      <c r="R26">
-        <v>1.87</v>
-      </c>
-      <c r="S26">
-        <v>1.57</v>
-      </c>
-      <c r="T26">
-        <v>2.48</v>
-      </c>
-      <c r="U26">
-        <v>3.6</v>
-      </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z26">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA26">
         <v>2.4</v>
       </c>
       <c r="AB26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC26">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
         <v>1.95</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,16 +4719,16 @@
         <v>2</v>
       </c>
       <c r="Q27">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U27">
         <v>3</v>
@@ -4740,34 +4740,34 @@
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
         <v>2.9</v>
       </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC27">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD27">
         <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5048,68 +5048,68 @@
         <v>3.75</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S29">
+        <v>1.4</v>
+      </c>
+      <c r="T29">
+        <v>2.75</v>
+      </c>
+      <c r="U29">
+        <v>3.03</v>
+      </c>
+      <c r="V29">
+        <v>1.3</v>
+      </c>
+      <c r="W29">
+        <v>1.06</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
         <v>1.33</v>
       </c>
-      <c r="T29">
-        <v>2.92</v>
-      </c>
-      <c r="U29">
-        <v>2.63</v>
-      </c>
-      <c r="V29">
-        <v>1.4</v>
-      </c>
-      <c r="W29">
-        <v>1.07</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.26</v>
-      </c>
       <c r="Z29">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
         <v>2.05</v>
       </c>
       <c r="AB29">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
-        <v>3.14</v>
+        <v>3.81</v>
       </c>
       <c r="AD29">
+        <v>1.24</v>
+      </c>
+      <c r="AE29">
+        <v>1.05</v>
+      </c>
+      <c r="AF29">
+        <v>1.85</v>
+      </c>
+      <c r="AG29">
+        <v>1.91</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.25</v>
+      </c>
+      <c r="AK29">
         <v>1.3</v>
-      </c>
-      <c r="AE29">
-        <v>1.07</v>
-      </c>
-      <c r="AF29">
-        <v>1.73</v>
-      </c>
-      <c r="AG29">
-        <v>2</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.67</v>
-      </c>
-      <c r="AK29">
-        <v>1.28</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.35</v>
+      </c>
+      <c r="O30">
+        <v>3.4</v>
+      </c>
+      <c r="P30">
+        <v>2.75</v>
+      </c>
+      <c r="Q30">
+        <v>2.85</v>
+      </c>
+      <c r="R30">
         <v>2.3</v>
       </c>
-      <c r="O30">
-        <v>3.45</v>
-      </c>
-      <c r="P30">
-        <v>2.62</v>
-      </c>
-      <c r="Q30">
-        <v>2.87</v>
-      </c>
-      <c r="R30">
-        <v>2.17</v>
-      </c>
       <c r="S30">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5232,10 +5232,10 @@
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
         <v>1.66</v>
@@ -5244,19 +5244,19 @@
         <v>2.16</v>
       </c>
       <c r="AC30">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AD30">
         <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O36">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q36">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R36">
         <v>2.28</v>
@@ -6195,13 +6195,13 @@
         <v>1.31</v>
       </c>
       <c r="T36">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6213,16 +6213,16 @@
         <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.86</v>
+        <v>3.55</v>
       </c>
       <c r="AA36">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD36">
         <v>1.37</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
+        <v>3.4</v>
+      </c>
+      <c r="O37">
         <v>3.6</v>
       </c>
-      <c r="O37">
-        <v>3.7</v>
-      </c>
       <c r="P37">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R37">
         <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
         <v>3.44</v>
       </c>
       <c r="U37">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6376,29 +6376,29 @@
         <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="AA37">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB37">
+        <v>2.21</v>
+      </c>
+      <c r="AC37">
+        <v>2.55</v>
+      </c>
+      <c r="AD37">
+        <v>1.48</v>
+      </c>
+      <c r="AE37">
+        <v>1.15</v>
+      </c>
+      <c r="AF37">
+        <v>1.53</v>
+      </c>
+      <c r="AG37">
         <v>2.25</v>
       </c>
-      <c r="AC37">
-        <v>2.54</v>
-      </c>
-      <c r="AD37">
-        <v>1.5</v>
-      </c>
-      <c r="AE37">
-        <v>1.14</v>
-      </c>
-      <c r="AF37">
-        <v>1.55</v>
-      </c>
-      <c r="AG37">
-        <v>2.3</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="AK37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.03</v>
@@ -6539,16 +6539,16 @@
         <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB38">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AC38">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD38">
         <v>1.5</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7321,16 +7321,16 @@
         <v>2.25</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q43">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.29</v>
@@ -7339,22 +7339,22 @@
         <v>3.25</v>
       </c>
       <c r="U43">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
         <v>1.52</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
         <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA43">
         <v>1.67</v>
@@ -7363,10 +7363,10 @@
         <v>2.15</v>
       </c>
       <c r="AC43">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD43">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
@@ -7375,7 +7375,7 @@
         <v>1.53</v>
       </c>
       <c r="AG43">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,61 +7481,61 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="O44">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="P44">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q44">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R44">
         <v>2.8</v>
       </c>
       <c r="S44">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V44">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA44">
         <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD44">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AG44">
         <v>1.62</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,46 +7644,46 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R45">
         <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="AA45">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB45">
         <v>1.75</v>
@@ -7701,7 +7701,7 @@
         <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>5.25</v>
+        <v>6.15</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S46">
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V46">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AD46">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG46">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK46">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>2.6</v>
       </c>
       <c r="R48">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -8154,10 +8154,10 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V48">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -8178,16 +8178,16 @@
         <v>3.3</v>
       </c>
       <c r="AC48">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD48">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AE48">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF48">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AG48">
         <v>3.2</v>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8471,22 +8471,22 @@
         <v>3.7</v>
       </c>
       <c r="R50">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S50">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T50">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U50">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.04</v>
@@ -8495,28 +8495,28 @@
         <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA50">
         <v>2.08</v>
       </c>
       <c r="AB50">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC50">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
         <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG50">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AK50">
         <v>1.3</v>
@@ -9274,31 +9274,31 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O55">
         <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="Q55">
         <v>3.1</v>
       </c>
       <c r="R55">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S55">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U55">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V55">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
         <v>1.06</v>
@@ -9310,10 +9310,10 @@
         <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AA55">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB55">
         <v>1.9</v>
@@ -9322,7 +9322,7 @@
         <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE55">
         <v>1.11</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
         <v>1.44</v>
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O56">
-        <v>5.85</v>
+        <v>6.15</v>
       </c>
       <c r="P56">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q56">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R56">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AA56">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
         <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE56">
         <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG56">
         <v>1.8</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK56">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3.59</v>
+        <v>3.86</v>
       </c>
       <c r="Q58">
+        <v>2.3</v>
+      </c>
+      <c r="R58">
+        <v>2.4</v>
+      </c>
+      <c r="S58">
+        <v>1.25</v>
+      </c>
+      <c r="T58">
+        <v>3.6</v>
+      </c>
+      <c r="U58">
         <v>2.38</v>
       </c>
-      <c r="R58">
-        <v>2.35</v>
-      </c>
-      <c r="S58">
-        <v>1.3</v>
-      </c>
-      <c r="T58">
-        <v>3.5</v>
-      </c>
-      <c r="U58">
-        <v>2.34</v>
-      </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9799,13 +9799,13 @@
         <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA58">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB58">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC58">
         <v>2.45</v>
@@ -9814,13 +9814,13 @@
         <v>1.53</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG58">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="O60">
         <v>3.1</v>
       </c>
       <c r="P60">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q60">
-        <v>3.49</v>
+        <v>3.12</v>
       </c>
       <c r="R60">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S60">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T60">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U60">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V60">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W60">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z60">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AA60">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AB60">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC60">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF60">
         <v>1.89</v>
       </c>
       <c r="AG60">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK60">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,43 +10252,43 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="O61">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P61">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q61">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R61">
         <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T61">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V61">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA61">
         <v>1.67</v>
@@ -10297,19 +10297,19 @@
         <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AD61">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O13">
         <v>3.1</v>
@@ -2437,55 +2437,55 @@
         <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R13">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
         <v>1.36</v>
@@ -2793,10 +2793,10 @@
         <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC15">
         <v>3.14</v>
@@ -2811,7 +2811,7 @@
         <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="R31">
         <v>2.3</v>
@@ -5380,46 +5380,46 @@
         <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC32">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AD32">
         <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="O33">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="P33">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="Q33">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R33">
         <v>3.08</v>
       </c>
       <c r="S33">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T33">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>1.75</v>
       </c>
       <c r="V33">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="W33">
         <v>1.25</v>
@@ -5727,25 +5727,25 @@
         <v>8</v>
       </c>
       <c r="AA33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AC33">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AD33">
         <v>2.1</v>
       </c>
       <c r="AE33">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O34">
         <v>4</v>
       </c>
       <c r="P34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -5872,43 +5872,43 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
         <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA34">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC34">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AD34">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="O35">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>6.65</v>
+        <v>7.38</v>
       </c>
       <c r="Q35">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R35">
         <v>2.5</v>
       </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
         <v>1.13</v>
@@ -6047,31 +6047,31 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="AA35">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="AC35">
         <v>2.27</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE35">
         <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -7164,55 +7164,55 @@
         <v>4.4</v>
       </c>
       <c r="Q42">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>3.24</v>
+        <v>3.11</v>
       </c>
       <c r="U42">
-        <v>2.33</v>
+        <v>2.73</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
         <v>1.1</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA42">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AB42">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG42">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
         <v>2.8</v>
@@ -9615,16 +9615,16 @@
         <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T57">
         <v>3.02</v>
       </c>
       <c r="U57">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V57">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W57">
         <v>1.09</v>
@@ -9636,10 +9636,10 @@
         <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>4.11</v>
+        <v>3.72</v>
       </c>
       <c r="AA57">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
         <v>2</v>
@@ -9648,10 +9648,10 @@
         <v>2.8</v>
       </c>
       <c r="AD57">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
         <v>1.6</v>
@@ -9935,43 +9935,43 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S59">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T59">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="U59">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V59">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="W59">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="AA59">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB59">
         <v>3.4</v>
       </c>
       <c r="AC59">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AD59">
         <v>2.05</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK59">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O64">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P64">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
         <v>3.05</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="U65">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="V65">
         <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AA65">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC65">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE65">
         <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG65">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK65">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="O66">
-        <v>4.16</v>
+        <v>4.55</v>
       </c>
       <c r="P66">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="Q66">
         <v>1.94</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
         <v>1.29</v>
@@ -11088,10 +11088,10 @@
         <v>3.28</v>
       </c>
       <c r="U66">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="V66">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z66">
         <v>4.3</v>
       </c>
       <c r="AA66">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB66">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD66">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE66">
         <v>1.17</v>
       </c>
       <c r="AF66">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG66">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>2.87</v>
       </c>
       <c r="Q68">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R68">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="U68">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V68">
         <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z68">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA68">
         <v>1.8</v>
@@ -11444,13 +11444,13 @@
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
         <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,31 +11556,31 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="O69">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P69">
-        <v>7.25</v>
+        <v>6.65</v>
       </c>
       <c r="Q69">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R69">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T69">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="U69">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="V69">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W69">
         <v>1.09</v>
@@ -11589,25 +11589,25 @@
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA69">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB69">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC69">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
         <v>1.85</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -3928,25 +3928,25 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA22">
         <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AC22">
         <v>2.38</v>
       </c>
       <c r="AD22">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF22">
         <v>1.44</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q31">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA31">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC31">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AD31">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="R32">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="AA32">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB32">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC32">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G64">
@@ -10744,61 +10744,61 @@
         <v>2.25</v>
       </c>
       <c r="O64">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P64">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q64">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R64">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="T64">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="U64">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="V64">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z64">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA64">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AB64">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC64">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AD64">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AG64">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O65">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P65">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S65">
+        <v>1.58</v>
+      </c>
+      <c r="T65">
+        <v>2.27</v>
+      </c>
+      <c r="U65">
+        <v>3.8</v>
+      </c>
+      <c r="V65">
+        <v>1.22</v>
+      </c>
+      <c r="W65">
+        <v>1.01</v>
+      </c>
+      <c r="X65">
+        <v>1.07</v>
+      </c>
+      <c r="Y65">
+        <v>1.5</v>
+      </c>
+      <c r="Z65">
+        <v>2.36</v>
+      </c>
+      <c r="AA65">
+        <v>2.41</v>
+      </c>
+      <c r="AB65">
         <v>1.44</v>
       </c>
-      <c r="T65">
-        <v>2.5</v>
-      </c>
-      <c r="U65">
-        <v>2.99</v>
-      </c>
-      <c r="V65">
-        <v>1.33</v>
-      </c>
-      <c r="W65">
-        <v>1.05</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.33</v>
-      </c>
-      <c r="Z65">
-        <v>2.83</v>
-      </c>
-      <c r="AA65">
-        <v>2.25</v>
-      </c>
-      <c r="AB65">
-        <v>1.6</v>
-      </c>
       <c r="AC65">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AD65">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG65">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK65">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11731,13 +11731,13 @@
         <v>3.12</v>
       </c>
       <c r="R70">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T70">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U70">
         <v>3</v>
@@ -11776,7 +11776,7 @@
         <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="P4">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
         <v>1.84</v>
@@ -988,25 +988,25 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Z4">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AA4">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AB4">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>6.37</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>1.07</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
         <v>1.38</v>
@@ -1622,10 +1622,10 @@
         <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="R8">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
         <v>1.48</v>
@@ -1649,19 +1649,19 @@
         <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB8">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
         <v>4.1</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>4.42</v>
+        <v>4.85</v>
       </c>
       <c r="Q9">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
         <v>1.38</v>
@@ -1797,22 +1797,22 @@
         <v>2.78</v>
       </c>
       <c r="U9">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
         <v>1.99</v>
@@ -1821,19 +1821,19 @@
         <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="O10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>3.71</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.35</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>2.23</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC12">
         <v>3.82</v>
@@ -2775,7 +2775,7 @@
         <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
         <v>1.36</v>
@@ -2923,7 +2923,7 @@
         <v>3.35</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
         <v>3.49</v>
@@ -2935,13 +2935,13 @@
         <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2968,13 +2968,13 @@
         <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
         <v>3.46</v>
@@ -3113,10 +3113,10 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
         <v>1.95</v>
@@ -3572,7 +3572,7 @@
         <v>5.75</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P20">
         <v>1.58</v>
@@ -3587,28 +3587,28 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
         <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O21">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="P21">
         <v>12</v>
@@ -3744,7 +3744,7 @@
         <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3768,7 +3768,7 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA21">
         <v>1.69</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
         <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
@@ -3940,7 +3940,7 @@
         <v>2.18</v>
       </c>
       <c r="AC22">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD22">
         <v>1.46</v>
@@ -4058,40 +4058,40 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O23">
         <v>4.1</v>
       </c>
       <c r="P23">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q23">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
         <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V23">
         <v>1.48</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
         <v>4.2</v>
@@ -4103,19 +4103,19 @@
         <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P26">
         <v>2.75</v>
       </c>
       <c r="Q26">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="R26">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S26">
         <v>1.5</v>
       </c>
       <c r="T26">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
         <v>3.3</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4601,10 +4601,10 @@
         <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG26">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>1.37</v>
       </c>
       <c r="T27">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
         <v>3</v>
@@ -4737,7 +4737,7 @@
         <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.06</v>
@@ -4752,7 +4752,7 @@
         <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
         <v>3.9</v>
@@ -4761,7 +4761,7 @@
         <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
         <v>1.83</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AK27">
         <v>1.25</v>
@@ -5087,13 +5087,13 @@
         <v>1.24</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
         <v>4.33</v>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>2.33</v>
       </c>
       <c r="S31">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
         <v>2.53</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q32">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
         <v>2.4</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK32">
         <v>1.62</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O36">
         <v>4</v>
       </c>
       <c r="P36">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="Q36">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R36">
         <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U36">
         <v>2.63</v>
@@ -6219,13 +6219,13 @@
         <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
         <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE36">
         <v>1.11</v>
@@ -6234,7 +6234,7 @@
         <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6361,10 +6361,10 @@
         <v>3.44</v>
       </c>
       <c r="U37">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
         <v>1.14</v>
@@ -6373,7 +6373,7 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
         <v>4.4</v>
@@ -6385,13 +6385,13 @@
         <v>2.21</v>
       </c>
       <c r="AC37">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AD37">
         <v>1.48</v>
       </c>
       <c r="AE37">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
         <v>1.53</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>1.22</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O38">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
       </c>
       <c r="R38">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
         <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
         <v>1.1</v>
@@ -6545,13 +6545,13 @@
         <v>1.62</v>
       </c>
       <c r="AB38">
+        <v>2.23</v>
+      </c>
+      <c r="AC38">
         <v>2.29</v>
       </c>
-      <c r="AC38">
-        <v>2.31</v>
-      </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE38">
         <v>1.18</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="O42">
         <v>3.65</v>
@@ -7164,10 +7164,10 @@
         <v>4.4</v>
       </c>
       <c r="Q42">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
         <v>1.35</v>
@@ -7182,10 +7182,10 @@
         <v>1.42</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
         <v>1.23</v>
@@ -7200,19 +7200,19 @@
         <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD42">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
         <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG42">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -7342,10 +7342,10 @@
         <v>2.5</v>
       </c>
       <c r="V43">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.04</v>
@@ -7354,7 +7354,7 @@
         <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="AA43">
         <v>1.67</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O44">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="P44">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q44">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R44">
         <v>2.8</v>
@@ -7499,25 +7499,25 @@
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W44">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>4.8</v>
+        <v>4.56</v>
       </c>
       <c r="AA44">
         <v>1.53</v>
@@ -7526,16 +7526,16 @@
         <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD44">
         <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG44">
         <v>1.62</v>
@@ -7644,16 +7644,16 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O45">
         <v>3.2</v>
       </c>
       <c r="P45">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="R45">
         <v>2.1</v>
@@ -7662,13 +7662,13 @@
         <v>1.38</v>
       </c>
       <c r="T45">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U45">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V45">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W45">
         <v>1.08</v>
@@ -7680,7 +7680,7 @@
         <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AA45">
         <v>2</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P46">
         <v>6.15</v>
@@ -7822,13 +7822,13 @@
         <v>2.17</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
         <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
         <v>1.47</v>
@@ -7837,7 +7837,7 @@
         <v>1.11</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
         <v>1.2</v>
@@ -7846,19 +7846,19 @@
         <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
         <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD46">
         <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
         <v>1.79</v>
@@ -8474,10 +8474,10 @@
         <v>2</v>
       </c>
       <c r="S50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T50">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U50">
         <v>3.16</v>
@@ -8486,10 +8486,10 @@
         <v>1.34</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.36</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.3</v>
@@ -9295,10 +9295,10 @@
         <v>2.88</v>
       </c>
       <c r="U55">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.06</v>
@@ -9328,7 +9328,7 @@
         <v>1.11</v>
       </c>
       <c r="AF55">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG55">
         <v>2.05</v>
@@ -9440,10 +9440,10 @@
         <v>1.24</v>
       </c>
       <c r="O56">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="P56">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -9455,13 +9455,13 @@
         <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9470,13 +9470,13 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA56">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB56">
         <v>2.25</v>
@@ -9491,10 +9491,10 @@
         <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG56">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
         <v>2.8</v>
@@ -9615,7 +9615,7 @@
         <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T57">
         <v>3.02</v>
@@ -9627,7 +9627,7 @@
         <v>1.47</v>
       </c>
       <c r="W57">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9636,16 +9636,16 @@
         <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA57">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB57">
         <v>2</v>
       </c>
       <c r="AC57">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD57">
         <v>1.37</v>
@@ -9657,7 +9657,7 @@
         <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -9817,10 +9817,10 @@
         <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O60">
         <v>3.1</v>
       </c>
       <c r="P60">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="Q60">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R60">
         <v>2.05</v>
@@ -10113,7 +10113,7 @@
         <v>3.28</v>
       </c>
       <c r="V60">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W60">
         <v>1.07</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O61">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>6.95</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -10267,28 +10267,28 @@
         <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
         <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="V61">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
         <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA61">
         <v>1.67</v>
@@ -10306,10 +10306,10 @@
         <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10759,25 +10759,25 @@
         <v>1.44</v>
       </c>
       <c r="T64">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U64">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="V64">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
         <v>1.05</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y64">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z64">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA64">
         <v>2.25</v>
@@ -10792,13 +10792,13 @@
         <v>1.2</v>
       </c>
       <c r="AE64">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF64">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG64">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O65">
         <v>2.87</v>
       </c>
       <c r="P65">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="Q65">
         <v>3.04</v>
@@ -10919,13 +10919,13 @@
         <v>1.83</v>
       </c>
       <c r="S65">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T65">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="U65">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="V65">
         <v>1.22</v>
@@ -10937,25 +10937,25 @@
         <v>1.07</v>
       </c>
       <c r="Y65">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z65">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AA65">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB65">
         <v>1.44</v>
       </c>
       <c r="AC65">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AD65">
         <v>1.13</v>
       </c>
       <c r="AE65">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF65">
         <v>2.05</v>
@@ -11728,13 +11728,13 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="R70">
         <v>2.05</v>
       </c>
       <c r="S70">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
         <v>2.58</v>
@@ -11758,7 +11758,7 @@
         <v>2.62</v>
       </c>
       <c r="AA70">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB70">
         <v>1.6</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK70">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU70"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,25 +982,25 @@
         <v>2.1</v>
       </c>
       <c r="U4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Y4">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z4">
         <v>2.16</v>
       </c>
       <c r="AA4">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AB4">
         <v>1.36</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
         <v>3.1</v>
@@ -2437,37 +2437,37 @@
         <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
         <v>1.81</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK13">
         <v>1.49</v>
@@ -3593,7 +3593,7 @@
         <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3744,7 +3744,7 @@
         <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3771,10 +3771,10 @@
         <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB21">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
         <v>2.88</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O22">
         <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
@@ -3910,16 +3910,16 @@
         <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
         <v>1.13</v>
@@ -3931,10 +3931,10 @@
         <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="AA22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB22">
         <v>2.18</v>
@@ -3946,7 +3946,7 @@
         <v>1.46</v>
       </c>
       <c r="AE22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
         <v>1.44</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="Q26">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="R26">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="AA26">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC26">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD26">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AK26">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.65</v>
+        <v>2.13</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3.75</v>
+      </c>
+      <c r="R28">
+        <v>2</v>
+      </c>
+      <c r="S28">
+        <v>1.4</v>
+      </c>
+      <c r="T28">
+        <v>2.75</v>
+      </c>
+      <c r="U28">
+        <v>3.03</v>
+      </c>
+      <c r="V28">
+        <v>1.3</v>
+      </c>
+      <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.33</v>
+      </c>
+      <c r="Z28">
         <v>3.1</v>
       </c>
-      <c r="P28">
-        <v>3.3</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
       <c r="AA28">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q29">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC29">
-        <v>3.81</v>
+        <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q30">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AC30">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q31">
-        <v>3.46</v>
+        <v>2.95</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T31">
         <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB31">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK31">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.13</v>
+        <v>1.15</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P32">
-        <v>2.38</v>
+        <v>14</v>
       </c>
       <c r="Q32">
-        <v>2.95</v>
+        <v>1.41</v>
       </c>
       <c r="R32">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA32">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AB32">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="AC32">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AG32">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AK32">
-        <v>1.62</v>
+        <v>5.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="O33">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="P33">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q33">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="S33">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="AD33">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>4.8</v>
+        <v>7.38</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -5875,40 +5875,40 @@
         <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>7.38</v>
+        <v>5.9</v>
       </c>
       <c r="Q35">
+        <v>1.97</v>
+      </c>
+      <c r="R35">
+        <v>2.28</v>
+      </c>
+      <c r="S35">
+        <v>1.34</v>
+      </c>
+      <c r="T35">
+        <v>2.91</v>
+      </c>
+      <c r="U35">
+        <v>2.63</v>
+      </c>
+      <c r="V35">
+        <v>1.47</v>
+      </c>
+      <c r="W35">
+        <v>1.07</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.22</v>
+      </c>
+      <c r="Z35">
+        <v>3.55</v>
+      </c>
+      <c r="AA35">
+        <v>1.72</v>
+      </c>
+      <c r="AB35">
+        <v>1.91</v>
+      </c>
+      <c r="AC35">
+        <v>2.8</v>
+      </c>
+      <c r="AD35">
+        <v>1.34</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
         <v>1.85</v>
       </c>
-      <c r="R35">
-        <v>2.5</v>
-      </c>
-      <c r="S35">
-        <v>1.22</v>
-      </c>
-      <c r="T35">
-        <v>3.8</v>
-      </c>
-      <c r="U35">
-        <v>2.2</v>
-      </c>
-      <c r="V35">
-        <v>1.6</v>
-      </c>
-      <c r="W35">
-        <v>1.13</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.14</v>
-      </c>
-      <c r="Z35">
-        <v>4.8</v>
-      </c>
-      <c r="AA35">
-        <v>1.53</v>
-      </c>
-      <c r="AB35">
-        <v>2.29</v>
-      </c>
-      <c r="AC35">
-        <v>2.27</v>
-      </c>
-      <c r="AD35">
-        <v>1.54</v>
-      </c>
-      <c r="AE35">
-        <v>1.2</v>
-      </c>
-      <c r="AF35">
-        <v>1.67</v>
-      </c>
       <c r="AG35">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>5.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q36">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>3.44</v>
       </c>
       <c r="U36">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>4.4</v>
+      </c>
+      <c r="AA36">
+        <v>1.63</v>
+      </c>
+      <c r="AB36">
+        <v>2.21</v>
+      </c>
+      <c r="AC36">
+        <v>2.46</v>
+      </c>
+      <c r="AD36">
+        <v>1.48</v>
+      </c>
+      <c r="AE36">
+        <v>1.19</v>
+      </c>
+      <c r="AF36">
+        <v>1.53</v>
+      </c>
+      <c r="AG36">
+        <v>2.25</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.2</v>
+      </c>
+      <c r="AK36">
         <v>1.22</v>
-      </c>
-      <c r="Z36">
-        <v>3.55</v>
-      </c>
-      <c r="AA36">
-        <v>1.72</v>
-      </c>
-      <c r="AB36">
-        <v>1.91</v>
-      </c>
-      <c r="AC36">
-        <v>2.8</v>
-      </c>
-      <c r="AD36">
-        <v>1.34</v>
-      </c>
-      <c r="AE36">
-        <v>1.11</v>
-      </c>
-      <c r="AF36">
-        <v>1.85</v>
-      </c>
-      <c r="AG36">
-        <v>1.86</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.17</v>
-      </c>
-      <c r="AK36">
-        <v>2.47</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="O37">
         <v>3.6</v>
       </c>
       <c r="P37">
-        <v>1.85</v>
+        <v>3.88</v>
       </c>
       <c r="Q37">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S37">
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB37">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AC37">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AD37">
         <v>1.48</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G40">
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 14:05:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
+        <v>2.2</v>
+      </c>
+      <c r="O42">
+        <v>3.4</v>
+      </c>
+      <c r="P42">
+        <v>2.7</v>
+      </c>
+      <c r="Q42">
+        <v>2.88</v>
+      </c>
+      <c r="R42">
+        <v>2.2</v>
+      </c>
+      <c r="S42">
+        <v>1.29</v>
+      </c>
+      <c r="T42">
+        <v>3.25</v>
+      </c>
+      <c r="U42">
+        <v>2.5</v>
+      </c>
+      <c r="V42">
+        <v>1.5</v>
+      </c>
+      <c r="W42">
+        <v>1.08</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.16</v>
+      </c>
+      <c r="Z42">
+        <v>4.4</v>
+      </c>
+      <c r="AA42">
+        <v>1.67</v>
+      </c>
+      <c r="AB42">
+        <v>2.15</v>
+      </c>
+      <c r="AC42">
+        <v>2.49</v>
+      </c>
+      <c r="AD42">
+        <v>1.42</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
         <v>1.53</v>
       </c>
-      <c r="O42">
-        <v>3.65</v>
-      </c>
-      <c r="P42">
-        <v>4.4</v>
-      </c>
-      <c r="Q42">
-        <v>2.2</v>
-      </c>
-      <c r="R42">
+      <c r="AG42">
         <v>2.25</v>
       </c>
-      <c r="S42">
-        <v>1.35</v>
-      </c>
-      <c r="T42">
-        <v>3.11</v>
-      </c>
-      <c r="U42">
-        <v>2.73</v>
-      </c>
-      <c r="V42">
-        <v>1.42</v>
-      </c>
-      <c r="W42">
-        <v>1.07</v>
-      </c>
-      <c r="X42">
-        <v>1.05</v>
-      </c>
-      <c r="Y42">
-        <v>1.23</v>
-      </c>
-      <c r="Z42">
-        <v>3.5</v>
-      </c>
-      <c r="AA42">
-        <v>1.83</v>
-      </c>
-      <c r="AB42">
-        <v>1.93</v>
-      </c>
-      <c r="AC42">
-        <v>3.1</v>
-      </c>
-      <c r="AD42">
-        <v>1.33</v>
-      </c>
-      <c r="AE42">
-        <v>1.11</v>
-      </c>
-      <c r="AF42">
-        <v>1.76</v>
-      </c>
-      <c r="AG42">
-        <v>1.96</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:00</t>
+          <t>2026-09-14 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="P43">
-        <v>2.7</v>
+        <v>15</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
         <v>3.25</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
+        <v>1.56</v>
+      </c>
+      <c r="W43">
+        <v>1.14</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.14</v>
+      </c>
+      <c r="Z43">
+        <v>4.56</v>
+      </c>
+      <c r="AA43">
+        <v>1.53</v>
+      </c>
+      <c r="AB43">
+        <v>2.3</v>
+      </c>
+      <c r="AC43">
+        <v>2.38</v>
+      </c>
+      <c r="AD43">
         <v>1.5</v>
       </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1.04</v>
-      </c>
-      <c r="Y43">
-        <v>1.16</v>
-      </c>
-      <c r="Z43">
-        <v>4.4</v>
-      </c>
-      <c r="AA43">
-        <v>1.67</v>
-      </c>
-      <c r="AB43">
-        <v>2.15</v>
-      </c>
-      <c r="AC43">
-        <v>2.49</v>
-      </c>
-      <c r="AD43">
-        <v>1.42</v>
-      </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG43">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.2</v>
+        <v>2.75</v>
       </c>
       <c r="O44">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>1.6</v>
+        <v>3.48</v>
       </c>
       <c r="R44">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="V44">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>4.56</v>
+        <v>2.88</v>
       </c>
       <c r="AA44">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD44">
+        <v>1.28</v>
+      </c>
+      <c r="AE44">
+        <v>1.08</v>
+      </c>
+      <c r="AF44">
+        <v>1.75</v>
+      </c>
+      <c r="AG44">
+        <v>1.95</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.5</v>
       </c>
-      <c r="AE44">
-        <v>1.18</v>
-      </c>
-      <c r="AF44">
-        <v>2.1</v>
-      </c>
-      <c r="AG44">
-        <v>1.62</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.01</v>
-      </c>
       <c r="AK44">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-14 14:30:00</t>
+          <t>2026-09-14 14:45:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
+        <v>1.44</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45">
+        <v>6.15</v>
+      </c>
+      <c r="Q45">
+        <v>2.06</v>
+      </c>
+      <c r="R45">
+        <v>2.17</v>
+      </c>
+      <c r="S45">
+        <v>1.26</v>
+      </c>
+      <c r="T45">
+        <v>3.25</v>
+      </c>
+      <c r="U45">
+        <v>2.38</v>
+      </c>
+      <c r="V45">
+        <v>1.47</v>
+      </c>
+      <c r="W45">
+        <v>1.11</v>
+      </c>
+      <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.2</v>
+      </c>
+      <c r="Z45">
+        <v>4.2</v>
+      </c>
+      <c r="AA45">
+        <v>1.66</v>
+      </c>
+      <c r="AB45">
+        <v>2.05</v>
+      </c>
+      <c r="AC45">
         <v>2.75</v>
       </c>
-      <c r="O45">
-        <v>3.2</v>
-      </c>
-      <c r="P45">
-        <v>2.5</v>
-      </c>
-      <c r="Q45">
-        <v>3.48</v>
-      </c>
-      <c r="R45">
-        <v>2.1</v>
-      </c>
-      <c r="S45">
+      <c r="AD45">
         <v>1.38</v>
       </c>
-      <c r="T45">
-        <v>2.83</v>
-      </c>
-      <c r="U45">
-        <v>2.99</v>
-      </c>
-      <c r="V45">
-        <v>1.34</v>
-      </c>
-      <c r="W45">
-        <v>1.08</v>
-      </c>
-      <c r="X45">
-        <v>1.03</v>
-      </c>
-      <c r="Y45">
-        <v>1.33</v>
-      </c>
-      <c r="Z45">
-        <v>2.88</v>
-      </c>
-      <c r="AA45">
-        <v>2</v>
-      </c>
-      <c r="AB45">
-        <v>1.75</v>
-      </c>
-      <c r="AC45">
-        <v>3.55</v>
-      </c>
-      <c r="AD45">
-        <v>1.28</v>
-      </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-14 14:45:00</t>
+          <t>2026-09-14 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>6.15</v>
+        <v>2.92</v>
       </c>
       <c r="Q46">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="R46">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>2</v>
+      </c>
+      <c r="V46">
+        <v>1.68</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>1.09</v>
+      </c>
+      <c r="Z46">
+        <v>6</v>
+      </c>
+      <c r="AA46">
+        <v>1.4</v>
+      </c>
+      <c r="AB46">
+        <v>2.7</v>
+      </c>
+      <c r="AC46">
+        <v>2.04</v>
+      </c>
+      <c r="AD46">
+        <v>1.68</v>
+      </c>
+      <c r="AE46">
         <v>1.26</v>
       </c>
-      <c r="T46">
-        <v>3.25</v>
-      </c>
-      <c r="U46">
-        <v>2.38</v>
-      </c>
-      <c r="V46">
-        <v>1.47</v>
-      </c>
-      <c r="W46">
-        <v>1.11</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.2</v>
-      </c>
-      <c r="Z46">
-        <v>4.2</v>
-      </c>
-      <c r="AA46">
-        <v>1.66</v>
-      </c>
-      <c r="AB46">
-        <v>2.05</v>
-      </c>
-      <c r="AC46">
+      <c r="AF46">
+        <v>1.37</v>
+      </c>
+      <c r="AG46">
         <v>2.75</v>
       </c>
-      <c r="AD46">
-        <v>1.38</v>
-      </c>
-      <c r="AE46">
-        <v>1.11</v>
-      </c>
-      <c r="AF46">
-        <v>1.79</v>
-      </c>
-      <c r="AG46">
-        <v>1.88</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R47">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -7991,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="V47">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -8003,31 +8003,31 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA47">
+        <v>1.28</v>
+      </c>
+      <c r="AB47">
+        <v>3.3</v>
+      </c>
+      <c r="AC47">
+        <v>1.73</v>
+      </c>
+      <c r="AD47">
+        <v>1.96</v>
+      </c>
+      <c r="AE47">
         <v>1.4</v>
       </c>
-      <c r="AB47">
-        <v>2.7</v>
-      </c>
-      <c r="AC47">
-        <v>2.04</v>
-      </c>
-      <c r="AD47">
-        <v>1.68</v>
-      </c>
-      <c r="AE47">
-        <v>1.26</v>
-      </c>
       <c r="AF47">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AG47">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -8154,10 +8154,10 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -8166,31 +8166,31 @@
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00:00</t>
+          <t>2026-09-14 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G49">
@@ -8305,55 +8305,55 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q50">
-        <v>3.7</v>
+        <v>2.23</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="U50">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
+        <v>3.65</v>
+      </c>
+      <c r="AA50">
+        <v>1.8</v>
+      </c>
+      <c r="AB50">
+        <v>1.87</v>
+      </c>
+      <c r="AC50">
         <v>3.1</v>
       </c>
-      <c r="AA50">
-        <v>2.08</v>
-      </c>
-      <c r="AB50">
-        <v>1.67</v>
-      </c>
-      <c r="AC50">
-        <v>3.77</v>
-      </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-14 15:30:00</t>
+          <t>2026-09-14 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q51">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R51">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U51">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q53">
-        <v>3.35</v>
+        <v>3.57</v>
       </c>
       <c r="R53">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA53">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB53">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK53">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54">
+        <v>3.1</v>
+      </c>
+      <c r="R54">
+        <v>2.15</v>
+      </c>
+      <c r="S54">
+        <v>1.36</v>
+      </c>
+      <c r="T54">
+        <v>2.88</v>
+      </c>
+      <c r="U54">
+        <v>2.75</v>
+      </c>
+      <c r="V54">
+        <v>1.36</v>
+      </c>
+      <c r="W54">
+        <v>1.06</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.3</v>
+      </c>
+      <c r="Z54">
+        <v>3.44</v>
+      </c>
+      <c r="AA54">
+        <v>1.87</v>
+      </c>
+      <c r="AB54">
+        <v>1.9</v>
+      </c>
+      <c r="AC54">
         <v>3.25</v>
       </c>
-      <c r="R54">
-        <v>2.17</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>2.55</v>
-      </c>
-      <c r="V54">
-        <v>1.42</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>1.22</v>
-      </c>
-      <c r="Z54">
-        <v>3.8</v>
-      </c>
-      <c r="AA54">
+      <c r="AD54">
+        <v>1.32</v>
+      </c>
+      <c r="AE54">
+        <v>1.11</v>
+      </c>
+      <c r="AF54">
         <v>1.75</v>
       </c>
-      <c r="AB54">
-        <v>1.92</v>
-      </c>
-      <c r="AC54">
-        <v>2.95</v>
-      </c>
-      <c r="AD54">
-        <v>1.34</v>
-      </c>
-      <c r="AE54">
-        <v>1.1</v>
-      </c>
-      <c r="AF54">
-        <v>1.58</v>
-      </c>
       <c r="AG54">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="O55">
+        <v>6.05</v>
+      </c>
+      <c r="P55">
+        <v>10</v>
+      </c>
+      <c r="Q55">
+        <v>1.67</v>
+      </c>
+      <c r="R55">
+        <v>2.9</v>
+      </c>
+      <c r="S55">
+        <v>1.27</v>
+      </c>
+      <c r="T55">
         <v>3.3</v>
       </c>
-      <c r="P55">
-        <v>2.63</v>
-      </c>
-      <c r="Q55">
-        <v>3.1</v>
-      </c>
-      <c r="R55">
-        <v>2.15</v>
-      </c>
-      <c r="S55">
-        <v>1.36</v>
-      </c>
-      <c r="T55">
-        <v>2.88</v>
-      </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="V55">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA55">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AB55">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AG55">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK55">
-        <v>1.44</v>
+        <v>3.61</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,65 +9437,65 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="O56">
-        <v>6.05</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="Q56">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="R56">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U56">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AB56">
+        <v>2</v>
+      </c>
+      <c r="AC56">
+        <v>2.83</v>
+      </c>
+      <c r="AD56">
+        <v>1.37</v>
+      </c>
+      <c r="AE56">
+        <v>1.14</v>
+      </c>
+      <c r="AF56">
+        <v>1.6</v>
+      </c>
+      <c r="AG56">
         <v>2.25</v>
       </c>
-      <c r="AC56">
-        <v>2.4</v>
-      </c>
-      <c r="AD56">
-        <v>1.56</v>
-      </c>
-      <c r="AE56">
-        <v>1.22</v>
-      </c>
-      <c r="AF56">
-        <v>2</v>
-      </c>
-      <c r="AG56">
-        <v>1.77</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>3.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-14 15:45:00</t>
+          <t>2026-09-14 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
+        <v>1.9</v>
+      </c>
+      <c r="O57">
+        <v>3.6</v>
+      </c>
+      <c r="P57">
+        <v>3.7</v>
+      </c>
+      <c r="Q57">
+        <v>2.3</v>
+      </c>
+      <c r="R57">
         <v>2.4</v>
       </c>
-      <c r="O57">
-        <v>3.5</v>
-      </c>
-      <c r="P57">
-        <v>2.95</v>
-      </c>
-      <c r="Q57">
-        <v>2.8</v>
-      </c>
-      <c r="R57">
-        <v>2.25</v>
-      </c>
       <c r="S57">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="U57">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V57">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
+        <v>1.15</v>
+      </c>
+      <c r="Z57">
+        <v>4.65</v>
+      </c>
+      <c r="AA57">
+        <v>1.6</v>
+      </c>
+      <c r="AB57">
+        <v>2.4</v>
+      </c>
+      <c r="AC57">
+        <v>2.45</v>
+      </c>
+      <c r="AD57">
+        <v>1.53</v>
+      </c>
+      <c r="AE57">
+        <v>1.22</v>
+      </c>
+      <c r="AF57">
+        <v>1.44</v>
+      </c>
+      <c r="AG57">
+        <v>2.63</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="Z57">
-        <v>3.9</v>
-      </c>
-      <c r="AA57">
-        <v>1.73</v>
-      </c>
-      <c r="AB57">
-        <v>2</v>
-      </c>
-      <c r="AC57">
-        <v>2.83</v>
-      </c>
-      <c r="AD57">
-        <v>1.37</v>
-      </c>
-      <c r="AE57">
-        <v>1.14</v>
-      </c>
-      <c r="AF57">
-        <v>1.6</v>
-      </c>
-      <c r="AG57">
-        <v>2.25</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.29</v>
-      </c>
       <c r="AK57">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>6.65</v>
       </c>
       <c r="P58">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="U58">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z58">
-        <v>4.65</v>
+        <v>9</v>
       </c>
       <c r="AA58">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AB58">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AC58">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="AD58">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK58">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:00</t>
+          <t>2026-09-14 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.21</v>
+        <v>2.36</v>
       </c>
       <c r="O59">
-        <v>6.45</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>8</v>
+        <v>2.99</v>
       </c>
       <c r="Q59">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="R59">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="U59">
-        <v>1.72</v>
+        <v>3.28</v>
       </c>
       <c r="V59">
-        <v>2.04</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="Z59">
-        <v>9</v>
+        <v>2.75</v>
       </c>
       <c r="AA59">
-        <v>1.22</v>
+        <v>2.27</v>
       </c>
       <c r="AB59">
-        <v>3.4</v>
+        <v>1.59</v>
       </c>
       <c r="AC59">
-        <v>1.63</v>
+        <v>3.9</v>
       </c>
       <c r="AD59">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AG59">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AK59">
-        <v>3.7</v>
+        <v>1.45</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,81 +10089,81 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="O60">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>2.99</v>
+        <v>6.95</v>
       </c>
       <c r="Q60">
+        <v>2</v>
+      </c>
+      <c r="R60">
+        <v>2.4</v>
+      </c>
+      <c r="S60">
+        <v>1.29</v>
+      </c>
+      <c r="T60">
         <v>3.3</v>
       </c>
-      <c r="R60">
-        <v>2.05</v>
-      </c>
-      <c r="S60">
+      <c r="U60">
+        <v>2.39</v>
+      </c>
+      <c r="V60">
+        <v>1.5</v>
+      </c>
+      <c r="W60">
+        <v>1.08</v>
+      </c>
+      <c r="X60">
+        <v>1.04</v>
+      </c>
+      <c r="Y60">
+        <v>1.2</v>
+      </c>
+      <c r="Z60">
+        <v>4.2</v>
+      </c>
+      <c r="AA60">
+        <v>1.67</v>
+      </c>
+      <c r="AB60">
+        <v>2.1</v>
+      </c>
+      <c r="AC60">
+        <v>2.76</v>
+      </c>
+      <c r="AD60">
         <v>1.44</v>
       </c>
-      <c r="T60">
-        <v>2.6</v>
-      </c>
-      <c r="U60">
-        <v>3.28</v>
-      </c>
-      <c r="V60">
-        <v>1.33</v>
-      </c>
-      <c r="W60">
-        <v>1.07</v>
-      </c>
-      <c r="X60">
-        <v>1.03</v>
-      </c>
-      <c r="Y60">
-        <v>1.41</v>
-      </c>
-      <c r="Z60">
+      <c r="AE60">
+        <v>1.17</v>
+      </c>
+      <c r="AF60">
+        <v>1.84</v>
+      </c>
+      <c r="AG60">
+        <v>1.95</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.2</v>
+      </c>
+      <c r="AK60">
         <v>2.75</v>
       </c>
-      <c r="AA60">
-        <v>2.27</v>
-      </c>
-      <c r="AB60">
-        <v>1.59</v>
-      </c>
-      <c r="AC60">
-        <v>3.9</v>
-      </c>
-      <c r="AD60">
-        <v>1.18</v>
-      </c>
-      <c r="AE60">
-        <v>1.02</v>
-      </c>
-      <c r="AF60">
-        <v>1.89</v>
-      </c>
-      <c r="AG60">
-        <v>1.84</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.4</v>
-      </c>
-      <c r="AK60">
-        <v>1.45</v>
-      </c>
       <c r="AL60">
         <v>0</v>
       </c>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-14 16:15:00</t>
+          <t>2026-09-14 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T61">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U61">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA61">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB61">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC61">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD61">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF61">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG61">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-14 16:45:00</t>
+          <t>2026-09-14 18:00:00</t>
         </is>
       </c>
     </row>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G62">
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10448,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-14 18:00:00</t>
+          <t>2026-09-14 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O64">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P64">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="Q64">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S64">
+        <v>1.55</v>
+      </c>
+      <c r="T64">
+        <v>2.37</v>
+      </c>
+      <c r="U64">
+        <v>3.9</v>
+      </c>
+      <c r="V64">
+        <v>1.22</v>
+      </c>
+      <c r="W64">
+        <v>1.01</v>
+      </c>
+      <c r="X64">
+        <v>1.07</v>
+      </c>
+      <c r="Y64">
+        <v>1.51</v>
+      </c>
+      <c r="Z64">
+        <v>2.34</v>
+      </c>
+      <c r="AA64">
+        <v>2.44</v>
+      </c>
+      <c r="AB64">
         <v>1.44</v>
       </c>
-      <c r="T64">
-        <v>2.56</v>
-      </c>
-      <c r="U64">
-        <v>2.95</v>
-      </c>
-      <c r="V64">
-        <v>1.34</v>
-      </c>
-      <c r="W64">
-        <v>1.05</v>
-      </c>
-      <c r="X64">
-        <v>1.08</v>
-      </c>
-      <c r="Y64">
-        <v>1.4</v>
-      </c>
-      <c r="Z64">
-        <v>2.75</v>
-      </c>
-      <c r="AA64">
-        <v>2.25</v>
-      </c>
-      <c r="AB64">
-        <v>1.6</v>
-      </c>
       <c r="AC64">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AD64">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF64">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG64">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.11</v>
+        <v>1.35</v>
       </c>
       <c r="O65">
-        <v>2.87</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>2.82</v>
+        <v>6.95</v>
       </c>
       <c r="Q65">
-        <v>3.04</v>
+        <v>1.94</v>
       </c>
       <c r="R65">
+        <v>2.43</v>
+      </c>
+      <c r="S65">
+        <v>1.29</v>
+      </c>
+      <c r="T65">
+        <v>3.28</v>
+      </c>
+      <c r="U65">
+        <v>2.36</v>
+      </c>
+      <c r="V65">
+        <v>1.5</v>
+      </c>
+      <c r="W65">
+        <v>1.1</v>
+      </c>
+      <c r="X65">
+        <v>1.02</v>
+      </c>
+      <c r="Y65">
+        <v>1.21</v>
+      </c>
+      <c r="Z65">
+        <v>4.3</v>
+      </c>
+      <c r="AA65">
+        <v>1.66</v>
+      </c>
+      <c r="AB65">
+        <v>2.1</v>
+      </c>
+      <c r="AC65">
+        <v>2.48</v>
+      </c>
+      <c r="AD65">
+        <v>1.43</v>
+      </c>
+      <c r="AE65">
+        <v>1.17</v>
+      </c>
+      <c r="AF65">
         <v>1.83</v>
       </c>
-      <c r="S65">
-        <v>1.55</v>
-      </c>
-      <c r="T65">
-        <v>2.37</v>
-      </c>
-      <c r="U65">
-        <v>3.9</v>
-      </c>
-      <c r="V65">
-        <v>1.22</v>
-      </c>
-      <c r="W65">
-        <v>1.01</v>
-      </c>
-      <c r="X65">
-        <v>1.07</v>
-      </c>
-      <c r="Y65">
-        <v>1.51</v>
-      </c>
-      <c r="Z65">
-        <v>2.34</v>
-      </c>
-      <c r="AA65">
-        <v>2.44</v>
-      </c>
-      <c r="AB65">
-        <v>1.44</v>
-      </c>
-      <c r="AC65">
-        <v>4.6</v>
-      </c>
-      <c r="AD65">
-        <v>1.13</v>
-      </c>
-      <c r="AE65">
-        <v>1</v>
-      </c>
-      <c r="AF65">
-        <v>2.05</v>
-      </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>4.55</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T66">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U66">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z66">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE66">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF66">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK66">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-14 20:00:00</t>
+          <t>2026-09-14 20:30:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P68">
-        <v>2.87</v>
+        <v>6.65</v>
       </c>
       <c r="Q68">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="R68">
         <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V68">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA68">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB68">
         <v>2</v>
       </c>
       <c r="AC68">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD68">
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG68">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK68">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-14 20:30:00</t>
+          <t>2026-09-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,61 +11556,61 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q69">
+        <v>3.18</v>
+      </c>
+      <c r="R69">
+        <v>2.05</v>
+      </c>
+      <c r="S69">
+        <v>1.44</v>
+      </c>
+      <c r="T69">
+        <v>2.58</v>
+      </c>
+      <c r="U69">
+        <v>3</v>
+      </c>
+      <c r="V69">
+        <v>1.33</v>
+      </c>
+      <c r="W69">
+        <v>1.04</v>
+      </c>
+      <c r="X69">
+        <v>1.05</v>
+      </c>
+      <c r="Y69">
+        <v>1.38</v>
+      </c>
+      <c r="Z69">
+        <v>2.62</v>
+      </c>
+      <c r="AA69">
+        <v>2.29</v>
+      </c>
+      <c r="AB69">
+        <v>1.6</v>
+      </c>
+      <c r="AC69">
+        <v>4.4</v>
+      </c>
+      <c r="AD69">
+        <v>1.18</v>
+      </c>
+      <c r="AE69">
+        <v>1.02</v>
+      </c>
+      <c r="AF69">
         <v>1.91</v>
-      </c>
-      <c r="R69">
-        <v>2.3</v>
-      </c>
-      <c r="S69">
-        <v>1.31</v>
-      </c>
-      <c r="T69">
-        <v>3.28</v>
-      </c>
-      <c r="U69">
-        <v>2.36</v>
-      </c>
-      <c r="V69">
-        <v>1.49</v>
-      </c>
-      <c r="W69">
-        <v>1.09</v>
-      </c>
-      <c r="X69">
-        <v>1.04</v>
-      </c>
-      <c r="Y69">
-        <v>1.25</v>
-      </c>
-      <c r="Z69">
-        <v>3.9</v>
-      </c>
-      <c r="AA69">
-        <v>1.69</v>
-      </c>
-      <c r="AB69">
-        <v>2.12</v>
-      </c>
-      <c r="AC69">
-        <v>3</v>
-      </c>
-      <c r="AD69">
-        <v>1.4</v>
-      </c>
-      <c r="AE69">
-        <v>1.12</v>
-      </c>
-      <c r="AF69">
-        <v>1.85</v>
       </c>
       <c r="AG69">
         <v>1.8</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AK69">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11659,169 +11659,6 @@
         <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
-        <is>
-          <t>2026-09-14 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>3.18</v>
-      </c>
-      <c r="R70">
-        <v>2.05</v>
-      </c>
-      <c r="S70">
-        <v>1.44</v>
-      </c>
-      <c r="T70">
-        <v>2.58</v>
-      </c>
-      <c r="U70">
-        <v>3</v>
-      </c>
-      <c r="V70">
-        <v>1.33</v>
-      </c>
-      <c r="W70">
-        <v>1.04</v>
-      </c>
-      <c r="X70">
-        <v>1.05</v>
-      </c>
-      <c r="Y70">
-        <v>1.38</v>
-      </c>
-      <c r="Z70">
-        <v>2.62</v>
-      </c>
-      <c r="AA70">
-        <v>2.29</v>
-      </c>
-      <c r="AB70">
-        <v>1.6</v>
-      </c>
-      <c r="AC70">
-        <v>4.4</v>
-      </c>
-      <c r="AD70">
-        <v>1.18</v>
-      </c>
-      <c r="AE70">
-        <v>1.02</v>
-      </c>
-      <c r="AF70">
-        <v>1.91</v>
-      </c>
-      <c r="AG70">
-        <v>1.8</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.38</v>
-      </c>
-      <c r="AK70">
-        <v>1.5</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-09-14 21:30:00</t>
         </is>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4716,7 +4716,7 @@
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R51">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>2.55</v>
+      </c>
+      <c r="V51">
+        <v>1.42</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>1.22</v>
+      </c>
+      <c r="Z51">
+        <v>3.8</v>
+      </c>
+      <c r="AA51">
+        <v>1.75</v>
+      </c>
+      <c r="AB51">
+        <v>1.92</v>
+      </c>
+      <c r="AC51">
+        <v>2.95</v>
+      </c>
+      <c r="AD51">
         <v>1.34</v>
       </c>
-      <c r="T51">
-        <v>2.99</v>
-      </c>
-      <c r="U51">
-        <v>2.4</v>
-      </c>
-      <c r="V51">
-        <v>1.46</v>
-      </c>
-      <c r="W51">
-        <v>1.06</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.21</v>
-      </c>
-      <c r="Z51">
-        <v>4.1</v>
-      </c>
-      <c r="AA51">
-        <v>1.8</v>
-      </c>
-      <c r="AB51">
-        <v>2.02</v>
-      </c>
-      <c r="AC51">
-        <v>2.85</v>
-      </c>
-      <c r="AD51">
-        <v>1.4</v>
-      </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q52">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R52">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB52">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,34 +8948,34 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Q53">
-        <v>3.57</v>
+        <v>3.35</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T53">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U53">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8984,28 +8984,28 @@
         <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC53">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
         <v>3.6</v>
@@ -9673,7 +9673,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>2.25</v>
       </c>
       <c r="O63">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P63">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -10596,13 +10596,13 @@
         <v>1.44</v>
       </c>
       <c r="T63">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U63">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="V63">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
         <v>1.05</v>
@@ -10632,10 +10632,10 @@
         <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG63">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
         <v>1.53</v>
@@ -10747,7 +10747,7 @@
         <v>2.87</v>
       </c>
       <c r="P64">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q64">
         <v>3.04</v>
@@ -10756,10 +10756,10 @@
         <v>1.83</v>
       </c>
       <c r="S64">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T64">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U64">
         <v>3.9</v>
@@ -10768,7 +10768,7 @@
         <v>1.22</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
         <v>1.07</v>
@@ -10792,7 +10792,7 @@
         <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
         <v>2.05</v>
@@ -11565,16 +11565,16 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R69">
         <v>2.05</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="U69">
         <v>3</v>
@@ -11595,7 +11595,7 @@
         <v>2.62</v>
       </c>
       <c r="AA69">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB69">
         <v>1.6</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -970,7 +970,7 @@
         <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
         <v>1.84</v>
@@ -982,7 +982,7 @@
         <v>2.1</v>
       </c>
       <c r="U4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V4">
         <v>1.15</v>
@@ -991,13 +991,13 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Y4">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z4">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AA4">
         <v>3.13</v>
@@ -1009,7 +1009,7 @@
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.66</v>
+      </c>
+      <c r="O8">
+        <v>3.45</v>
+      </c>
+      <c r="P8">
+        <v>4.85</v>
+      </c>
+      <c r="Q8">
+        <v>2.25</v>
+      </c>
+      <c r="R8">
         <v>2.09</v>
       </c>
-      <c r="O8">
-        <v>3.1</v>
-      </c>
-      <c r="P8">
-        <v>3.2</v>
-      </c>
-      <c r="Q8">
-        <v>2.69</v>
-      </c>
-      <c r="R8">
-        <v>1.93</v>
-      </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AA8">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="AB8">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>4.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="U9">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="AB9">
+        <v>1.58</v>
+      </c>
+      <c r="AC9">
+        <v>4.1</v>
+      </c>
+      <c r="AD9">
+        <v>1.2</v>
+      </c>
+      <c r="AE9">
+        <v>1.01</v>
+      </c>
+      <c r="AF9">
+        <v>1.94</v>
+      </c>
+      <c r="AG9">
         <v>1.77</v>
       </c>
-      <c r="AC9">
-        <v>3.34</v>
-      </c>
-      <c r="AD9">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.27</v>
       </c>
-      <c r="AE9">
-        <v>1.05</v>
-      </c>
-      <c r="AF9">
-        <v>1.92</v>
-      </c>
-      <c r="AG9">
-        <v>1.79</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.19</v>
-      </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
         <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1972,10 +1972,10 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
@@ -1993,7 +1993,7 @@
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="R16">
         <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
         <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2953,13 +2953,13 @@
         <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
@@ -2971,7 +2971,7 @@
         <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
         <v>2</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AK16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3442,19 +3442,19 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
         <v>2.12</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3463,7 +3463,7 @@
         <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3575,7 +3575,7 @@
         <v>4</v>
       </c>
       <c r="P20">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q20">
         <v>5.4</v>
@@ -3587,28 +3587,28 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3623,10 +3623,10 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3735,22 +3735,22 @@
         <v>1.21</v>
       </c>
       <c r="O21">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Q21">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R21">
         <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
         <v>2.38</v>
@@ -3759,7 +3759,7 @@
         <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.04</v>
@@ -3768,22 +3768,22 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AA21">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB21">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AC21">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
         <v>2.32</v>
@@ -3898,7 +3898,7 @@
         <v>2.49</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
         <v>2.46</v>
@@ -3910,16 +3910,16 @@
         <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T22">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W22">
         <v>1.13</v>
@@ -3928,44 +3928,44 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="AA22">
         <v>1.62</v>
       </c>
       <c r="AB22">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC22">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
         <v>1.15</v>
       </c>
       <c r="AF22">
+        <v>1.5</v>
+      </c>
+      <c r="AG22">
+        <v>2.34</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.44</v>
-      </c>
-      <c r="AG22">
-        <v>2.38</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>1.53</v>
@@ -4061,10 +4061,10 @@
         <v>5.5</v>
       </c>
       <c r="O23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -4073,25 +4073,25 @@
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U23">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
         <v>4.2</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="AK23">
         <v>1.16</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q25">
         <v>3.36</v>
       </c>
       <c r="R25">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S25">
         <v>1.5</v>
@@ -4405,7 +4405,7 @@
         <v>2.5</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V25">
         <v>1.25</v>
@@ -4414,7 +4414,7 @@
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
         <v>1.42</v>
@@ -4423,10 +4423,10 @@
         <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC25">
         <v>4.75</v>
@@ -4435,13 +4435,13 @@
         <v>1.15</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -6023,25 +6023,25 @@
         <v>5.9</v>
       </c>
       <c r="Q35">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
         <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
         <v>2.91</v>
       </c>
       <c r="U35">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.04</v>
@@ -6053,25 +6053,25 @@
         <v>3.55</v>
       </c>
       <c r="AA35">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB35">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AC35">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AD35">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>3.4</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
         <v>1.85</v>
@@ -6189,7 +6189,7 @@
         <v>3.8</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6198,13 +6198,13 @@
         <v>3.44</v>
       </c>
       <c r="U36">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.03</v>
@@ -6219,19 +6219,19 @@
         <v>1.63</v>
       </c>
       <c r="AB36">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
         <v>2.46</v>
       </c>
       <c r="AD36">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
         <v>2.25</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S37">
         <v>1.25</v>
@@ -6367,7 +6367,7 @@
         <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6376,22 +6376,22 @@
         <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA37">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD37">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.29</v>
@@ -7179,10 +7179,10 @@
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
         <v>1.04</v>
@@ -7191,7 +7191,7 @@
         <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
@@ -7206,7 +7206,7 @@
         <v>1.42</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
         <v>1.53</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="O43">
         <v>5.75</v>
@@ -7327,7 +7327,7 @@
         <v>15</v>
       </c>
       <c r="Q43">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R43">
         <v>2.8</v>
@@ -7336,10 +7336,10 @@
         <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V43">
         <v>1.56</v>
@@ -7351,16 +7351,16 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC43">
         <v>2.38</v>
@@ -7372,7 +7372,7 @@
         <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG43">
         <v>1.62</v>
@@ -7490,7 +7490,7 @@
         <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7499,31 +7499,31 @@
         <v>1.38</v>
       </c>
       <c r="T44">
+        <v>2.88</v>
+      </c>
+      <c r="U44">
         <v>2.83</v>
       </c>
-      <c r="U44">
-        <v>2.99</v>
-      </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
         <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
         <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AA44">
         <v>2</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
         <v>3.55</v>
@@ -7554,7 +7554,7 @@
         <v>1.5</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,37 +7653,37 @@
         <v>6.15</v>
       </c>
       <c r="Q45">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
         <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
         <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
@@ -7692,13 +7692,13 @@
         <v>2.75</v>
       </c>
       <c r="AD45">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG45">
         <v>1.88</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P46">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -7822,31 +7822,31 @@
         <v>2.55</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V46">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z46">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
         <v>2.7</v>
@@ -7855,16 +7855,16 @@
         <v>2.04</v>
       </c>
       <c r="AD46">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE46">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF46">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG46">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P47">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -7985,31 +7985,31 @@
         <v>2.75</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U47">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V47">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z47">
         <v>7.5</v>
       </c>
       <c r="AA47">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB47">
         <v>3.3</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
         <v>1.55</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U49">
         <v>3.16</v>
@@ -8323,10 +8323,10 @@
         <v>1.34</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.36</v>
@@ -8341,10 +8341,10 @@
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
@@ -8353,7 +8353,7 @@
         <v>1.74</v>
       </c>
       <c r="AG49">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AK49">
         <v>1.3</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.23</v>
+        <v>3.25</v>
       </c>
       <c r="R50">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
         <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC50">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD50">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q51">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R51">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U51">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB51">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Q52">
-        <v>3.57</v>
+        <v>3.35</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U52">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,28 +8821,28 @@
         <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK52">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
+        <v>4.55</v>
+      </c>
+      <c r="Q53">
+        <v>2.23</v>
+      </c>
+      <c r="R53">
         <v>2.19</v>
       </c>
-      <c r="Q53">
-        <v>3.35</v>
-      </c>
-      <c r="R53">
-        <v>2.14</v>
-      </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
         <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC53">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O55">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="P55">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
       </c>
       <c r="R55">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="S55">
         <v>1.27</v>
@@ -9298,7 +9298,7 @@
         <v>2.16</v>
       </c>
       <c r="V55">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
         <v>1.13</v>
@@ -9316,7 +9316,7 @@
         <v>1.48</v>
       </c>
       <c r="AB55">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AC55">
         <v>2.4</v>
@@ -9328,10 +9328,10 @@
         <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG55">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P59">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
         <v>3.3</v>
@@ -9941,10 +9941,10 @@
         <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U59">
         <v>3.28</v>
@@ -9953,13 +9953,13 @@
         <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
         <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z59">
         <v>2.75</v>
@@ -9977,13 +9977,13 @@
         <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
         <v>1.89</v>
       </c>
       <c r="AG59">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK59">
         <v>1.45</v>
@@ -10092,13 +10092,13 @@
         <v>1.41</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P60">
-        <v>6.95</v>
+        <v>6.65</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R60">
         <v>2.4</v>
@@ -10110,10 +10110,10 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10125,28 +10125,28 @@
         <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC60">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE60">
         <v>1.17</v>
       </c>
       <c r="AF60">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
         <v>2.75</v>
@@ -10587,25 +10587,25 @@
         <v>3.1</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T63">
         <v>2.62</v>
       </c>
       <c r="U63">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W63">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1.08</v>
@@ -10617,16 +10617,16 @@
         <v>2.75</v>
       </c>
       <c r="AA63">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB63">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC63">
         <v>4.33</v>
       </c>
       <c r="AD63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
         <v>1.06</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10747,28 +10747,28 @@
         <v>2.87</v>
       </c>
       <c r="P64">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>3.04</v>
+        <v>2.84</v>
       </c>
       <c r="R64">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T64">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="U64">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="V64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X64">
         <v>1.07</v>
@@ -10780,7 +10780,7 @@
         <v>2.34</v>
       </c>
       <c r="AA64">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AB64">
         <v>1.44</v>
@@ -10792,7 +10792,7 @@
         <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF64">
         <v>2.05</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>1.35</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="P65">
         <v>6.95</v>
@@ -10916,7 +10916,7 @@
         <v>1.94</v>
       </c>
       <c r="R65">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="S65">
         <v>1.29</v>
@@ -10955,7 +10955,7 @@
         <v>1.43</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
         <v>1.83</v>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="R69">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="S69">
         <v>1.45</v>
@@ -11577,13 +11577,13 @@
         <v>2.53</v>
       </c>
       <c r="U69">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V69">
         <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.05</v>
@@ -11613,7 +11613,7 @@
         <v>1.91</v>
       </c>
       <c r="AG69">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
         <v>3.45</v>
       </c>
       <c r="P8">
-        <v>4.85</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -1637,7 +1637,7 @@
         <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
         <v>3.2</v>
@@ -1794,7 +1794,7 @@
         <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
         <v>3.28</v>
@@ -1812,19 +1812,19 @@
         <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA9">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="R12">
         <v>1.96</v>
@@ -2283,7 +2283,7 @@
         <v>1.47</v>
       </c>
       <c r="T12">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U12">
         <v>3.27</v>
@@ -2298,19 +2298,19 @@
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z12">
         <v>2.74</v>
       </c>
       <c r="AA12">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AB12">
         <v>1.64</v>
       </c>
       <c r="AC12">
-        <v>3.82</v>
+        <v>4.06</v>
       </c>
       <c r="AD12">
         <v>1.19</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="AK12">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="U13">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="V13">
         <v>1.39</v>
@@ -2458,7 +2458,7 @@
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.27</v>
@@ -2467,7 +2467,7 @@
         <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB13">
         <v>1.81</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
         <v>1.49</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O15">
+        <v>3.35</v>
+      </c>
+      <c r="P15">
         <v>3.25</v>
-      </c>
-      <c r="P15">
-        <v>3.31</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2793,10 +2793,10 @@
         <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB15">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
         <v>3.14</v>
@@ -2811,7 +2811,7 @@
         <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O17">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="P17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q17">
-        <v>3.7</v>
+        <v>5.02</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="U17">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
         <v>1.05</v>
@@ -3113,31 +3113,31 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG17">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T26">
         <v>2.63</v>
@@ -4571,10 +4571,10 @@
         <v>3</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.06</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="O27">
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4885,7 +4885,7 @@
         <v>3.75</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -5045,31 +5045,31 @@
         <v>2.62</v>
       </c>
       <c r="Q29">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
         <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
         <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
         <v>4.33</v>
@@ -5081,7 +5081,7 @@
         <v>2.16</v>
       </c>
       <c r="AC29">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AD29">
         <v>1.42</v>
@@ -5214,16 +5214,16 @@
         <v>2.33</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U30">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5232,7 +5232,7 @@
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
         <v>3.72</v>
@@ -5241,13 +5241,13 @@
         <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>2.84</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
         <v>1.11</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK30">
         <v>1.4</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="O31">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q31">
         <v>2.95</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
         <v>1.31</v>
@@ -5383,10 +5383,10 @@
         <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5413,7 +5413,7 @@
         <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O32">
-        <v>8.550000000000001</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q32">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R32">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="S32">
         <v>1.11</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="U32">
         <v>1.75</v>
@@ -5558,13 +5558,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z32">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA32">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AB32">
         <v>3.6</v>
@@ -5573,13 +5573,13 @@
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AE32">
         <v>1.5</v>
       </c>
       <c r="AF32">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
         <v>2.05</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>5.1</v>
+        <v>4.14</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,25 +5694,25 @@
         <v>3.95</v>
       </c>
       <c r="P33">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R33">
         <v>2.54</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
         <v>1.12</v>
@@ -5727,7 +5727,7 @@
         <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB33">
         <v>2.25</v>
@@ -5857,7 +5857,7 @@
         <v>4.6</v>
       </c>
       <c r="P34">
-        <v>7.38</v>
+        <v>6.5</v>
       </c>
       <c r="Q34">
         <v>1.85</v>
@@ -5872,7 +5872,7 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V34">
         <v>1.6</v>
@@ -5884,7 +5884,7 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
         <v>4.8</v>
@@ -5893,7 +5893,7 @@
         <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC34">
         <v>2.27</v>
@@ -5908,7 +5908,7 @@
         <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
         <v>3.65</v>
@@ -7001,10 +7001,10 @@
         <v>4.4</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.35</v>
@@ -7034,7 +7034,7 @@
         <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
         <v>3.1</v>
@@ -7046,10 +7046,10 @@
         <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         <v>2.8</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q51">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U51">
         <v>2.48</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.21</v>
@@ -8661,7 +8661,7 @@
         <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB51">
         <v>1.95</v>
@@ -8670,16 +8670,16 @@
         <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.19</v>
+        <v>4.4</v>
       </c>
       <c r="Q52">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>4.55</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
-        <v>2.23</v>
+        <v>3.35</v>
       </c>
       <c r="R53">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
         <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB53">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9123,19 +9123,19 @@
         <v>3.1</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S54">
         <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="U54">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.06</v>
@@ -9144,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z54">
         <v>3.44</v>
@@ -9159,16 +9159,16 @@
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9440,7 +9440,7 @@
         <v>2.4</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
         <v>2.95</v>
@@ -9464,7 +9464,7 @@
         <v>1.47</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9479,16 +9479,16 @@
         <v>1.73</v>
       </c>
       <c r="AB56">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC56">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD56">
         <v>1.37</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF56">
         <v>1.6</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
         <v>1.55</v>
@@ -9609,16 +9609,16 @@
         <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="R57">
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
         <v>2.38</v>
@@ -9627,7 +9627,7 @@
         <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9636,28 +9636,28 @@
         <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG57">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O58">
-        <v>6.65</v>
+        <v>6.3</v>
       </c>
       <c r="P58">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q58">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R58">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="S58">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T58">
         <v>5.5</v>
       </c>
       <c r="U58">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V58">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="W58">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X58">
         <v>0</v>
@@ -9802,7 +9802,7 @@
         <v>9</v>
       </c>
       <c r="AA58">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AB58">
         <v>3.4</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK58">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q61">
         <v>2.5</v>
@@ -10587,7 +10587,7 @@
         <v>3.1</v>
       </c>
       <c r="Q63">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="R63">
         <v>2.05</v>
@@ -10596,7 +10596,7 @@
         <v>1.42</v>
       </c>
       <c r="T63">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
         <v>2.85</v>
@@ -10632,10 +10632,10 @@
         <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AG63">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
         <v>1.82</v>
@@ -10762,7 +10762,7 @@
         <v>2.55</v>
       </c>
       <c r="U64">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="V64">
         <v>1.25</v>
@@ -10792,7 +10792,7 @@
         <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
         <v>2.05</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK64">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10916,7 +10916,7 @@
         <v>1.94</v>
       </c>
       <c r="R65">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
         <v>1.29</v>
@@ -10934,7 +10934,7 @@
         <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.21</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
+        <v>2.49</v>
+      </c>
+      <c r="O66">
+        <v>3.25</v>
+      </c>
+      <c r="P66">
         <v>2.55</v>
-      </c>
-      <c r="O66">
-        <v>3.35</v>
-      </c>
-      <c r="P66">
-        <v>2.6</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S67">
         <v>1.32</v>
@@ -11257,7 +11257,7 @@
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.04</v>
@@ -11272,7 +11272,7 @@
         <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
         <v>2.95</v>
@@ -11281,7 +11281,7 @@
         <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
         <v>1.62</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1.44</v>
       </c>
       <c r="O68">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P68">
         <v>6.65</v>
@@ -11414,10 +11414,10 @@
         <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W68">
         <v>1.09</v>
@@ -11426,7 +11426,7 @@
         <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
         <v>3.9</v>
@@ -11435,16 +11435,16 @@
         <v>1.69</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC68">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD68">
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
         <v>1.85</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK68">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="R69">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S69">
         <v>1.45</v>
@@ -11595,7 +11595,7 @@
         <v>2.62</v>
       </c>
       <c r="AA69">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB69">
         <v>1.6</v>
@@ -11613,7 +11613,7 @@
         <v>1.91</v>
       </c>
       <c r="AG69">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK69">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="R8">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
+        <v>1.57</v>
+      </c>
+      <c r="AC8">
+        <v>4.15</v>
+      </c>
+      <c r="AD8">
+        <v>1.16</v>
+      </c>
+      <c r="AE8">
+        <v>1.01</v>
+      </c>
+      <c r="AF8">
+        <v>1.94</v>
+      </c>
+      <c r="AG8">
         <v>1.77</v>
       </c>
-      <c r="AC8">
-        <v>3.34</v>
-      </c>
-      <c r="AD8">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.27</v>
       </c>
-      <c r="AE8">
-        <v>1.05</v>
-      </c>
-      <c r="AF8">
-        <v>1.92</v>
-      </c>
-      <c r="AG8">
-        <v>1.79</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.19</v>
-      </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="Q9">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
         <v>2.63</v>
@@ -4571,10 +4571,10 @@
         <v>3</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.06</v>
@@ -4713,10 +4713,10 @@
         <v>2.02</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>3.77</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>4.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q52">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="R52">
         <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W52">
+        <v>1.06</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.24</v>
+      </c>
+      <c r="Z52">
+        <v>3.75</v>
+      </c>
+      <c r="AA52">
+        <v>1.76</v>
+      </c>
+      <c r="AB52">
+        <v>2.02</v>
+      </c>
+      <c r="AC52">
+        <v>2.76</v>
+      </c>
+      <c r="AD52">
+        <v>1.4</v>
+      </c>
+      <c r="AE52">
         <v>1.1</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.25</v>
-      </c>
-      <c r="Z52">
-        <v>3.65</v>
-      </c>
-      <c r="AA52">
-        <v>1.9</v>
-      </c>
-      <c r="AB52">
-        <v>1.87</v>
-      </c>
-      <c r="AC52">
-        <v>3.22</v>
-      </c>
-      <c r="AD52">
-        <v>1.28</v>
-      </c>
-      <c r="AE52">
-        <v>1.07</v>
-      </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>4.4</v>
       </c>
       <c r="Q53">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="R53">
         <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB53">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC53">
-        <v>2.76</v>
+        <v>3.22</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1948,16 +1948,16 @@
         <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
         <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1972,7 +1972,7 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
         <v>3.75</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O20">
         <v>4</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q20">
         <v>5.4</v>
@@ -3590,7 +3590,7 @@
         <v>2.82</v>
       </c>
       <c r="U20">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -3599,7 +3599,7 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
@@ -3608,7 +3608,7 @@
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3623,10 +3623,10 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
         <v>2.38</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK21">
         <v>3.85</v>
@@ -5066,7 +5066,7 @@
         <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.18</v>
@@ -5761,7 +5761,7 @@
         <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>1.43</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P34">
         <v>6.5</v>
@@ -5896,7 +5896,7 @@
         <v>2.45</v>
       </c>
       <c r="AC34">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD34">
         <v>1.54</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>6.15</v>
+        <v>7.2</v>
       </c>
       <c r="Q45">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
         <v>1.26</v>
@@ -7665,16 +7665,16 @@
         <v>3.3</v>
       </c>
       <c r="U45">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
         <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
@@ -7683,22 +7683,22 @@
         <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD45">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG45">
         <v>1.88</v>
@@ -7717,7 +7717,7 @@
         <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8314,7 +8314,7 @@
         <v>1.45</v>
       </c>
       <c r="T49">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U49">
         <v>3.16</v>
@@ -8335,16 +8335,16 @@
         <v>3.1</v>
       </c>
       <c r="AA49">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB49">
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AK49">
         <v>1.3</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.37</v>
+        <v>4.4</v>
       </c>
       <c r="Q52">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="R52">
         <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>2.76</v>
+        <v>3.22</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>4.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="R53">
         <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
+        <v>1.06</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.24</v>
+      </c>
+      <c r="Z53">
+        <v>3.75</v>
+      </c>
+      <c r="AA53">
+        <v>1.76</v>
+      </c>
+      <c r="AB53">
+        <v>2.02</v>
+      </c>
+      <c r="AC53">
+        <v>2.76</v>
+      </c>
+      <c r="AD53">
+        <v>1.4</v>
+      </c>
+      <c r="AE53">
         <v>1.1</v>
       </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.25</v>
-      </c>
-      <c r="Z53">
-        <v>3.65</v>
-      </c>
-      <c r="AA53">
-        <v>1.9</v>
-      </c>
-      <c r="AB53">
-        <v>1.87</v>
-      </c>
-      <c r="AC53">
-        <v>3.22</v>
-      </c>
-      <c r="AD53">
-        <v>1.28</v>
-      </c>
-      <c r="AE53">
-        <v>1.07</v>
-      </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="O54">
         <v>3.3</v>
       </c>
       <c r="P54">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
       </c>
       <c r="R54">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S54">
         <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
         <v>1.06</v>
@@ -9150,22 +9150,22 @@
         <v>3.44</v>
       </c>
       <c r="AA54">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG54">
         <v>2</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9283,7 +9283,7 @@
         <v>10.5</v>
       </c>
       <c r="Q55">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R55">
         <v>2.92</v>
@@ -9331,7 +9331,7 @@
         <v>2</v>
       </c>
       <c r="AG55">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O57">
         <v>3.6</v>
@@ -9609,46 +9609,46 @@
         <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U57">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V57">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
         <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
@@ -9673,7 +9673,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
